--- a/Lab_python/lab4_new/lab4.5_new/lab4.5_new/прогноз_по_товарам.xlsx
+++ b/Lab_python/lab4_new/lab4.5_new/lab4.5_new/прогноз_по_товарам.xlsx
@@ -457,29 +457,29 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4235711</v>
+        <v>4164778</v>
       </c>
       <c r="C2" t="n">
-        <v>4238929</v>
+        <v>3988649</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Телевизоры</t>
+          <t>Ноутбуки</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3359743</v>
+        <v>3639314</v>
       </c>
       <c r="C3" t="n">
-        <v>3414764</v>
+        <v>4036479</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="4">
@@ -489,29 +489,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4416866</v>
+        <v>3940562</v>
       </c>
       <c r="C4" t="n">
-        <v>4109574</v>
+        <v>4037594</v>
       </c>
       <c r="D4" t="n">
-        <v>-7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ноутбуки</t>
+          <t>Телевизоры</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4128616</v>
+        <v>4707406</v>
       </c>
       <c r="C5" t="n">
-        <v>3888427</v>
+        <v>4608771</v>
       </c>
       <c r="D5" t="n">
-        <v>-5.8</v>
+        <v>-2.1</v>
       </c>
     </row>
   </sheetData>

--- a/Lab_python/lab4_new/lab4.5_new/lab4.5_new/прогноз_по_товарам.xlsx
+++ b/Lab_python/lab4_new/lab4.5_new/lab4.5_new/прогноз_по_товарам.xlsx
@@ -453,65 +453,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Планшеты</t>
+          <t>Ноутбуки</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4164778</v>
+        <v>202591</v>
       </c>
       <c r="C2" t="n">
-        <v>3988649</v>
+        <v>160534</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.2</v>
+        <v>-20.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ноутбуки</t>
+          <t>Планшеты</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3639314</v>
+        <v>183350</v>
       </c>
       <c r="C3" t="n">
-        <v>4036479</v>
+        <v>203722</v>
       </c>
       <c r="D3" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Смартфоны</t>
+          <t>Телевизоры</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3940562</v>
+        <v>169157</v>
       </c>
       <c r="C4" t="n">
-        <v>4037594</v>
+        <v>202991</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Телевизоры</t>
+          <t>Смартфоны</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4707406</v>
+        <v>145801</v>
       </c>
       <c r="C5" t="n">
-        <v>4608771</v>
+        <v>110303</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1</v>
+        <v>-24.3</v>
       </c>
     </row>
   </sheetData>
